--- a/光伏配储项目/电价数据/2026/松厦站.xlsx
+++ b/光伏配储项目/电价数据/2026/松厦站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5118199999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7579199999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5989800000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44558</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42387</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41262</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12812</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10425</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11845</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10797</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13061</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04899</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15683</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.20256</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09128</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15239</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.43546</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23889</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.18275</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.54496</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14297</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40078</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28325</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.39149</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21253</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.63993</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56426</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.32971</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40933</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.61575</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46324</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5776699999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63488</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8205</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6395599999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6519299999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79364</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.14763</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42902</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6849</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60024</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8206</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.66525</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6812999999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6508700000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6206699999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47719</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48132</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42615</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70756</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80413</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.55438</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.86676</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53659</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51802</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5086700000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48718</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49774</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7534400000000001</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42828</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5211699999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17083</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06103</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50246</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76707</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.16617</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.79622</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.53891</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5133099999999999</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26484</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.13028</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.4593</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.2892</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43073</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.63935</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78503</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.6204</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.23576</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7900700000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7391</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66495</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.60499</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77438</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.56645</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.08248</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47017</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.67635</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3347</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51752</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52415</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46078</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.47756</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27106</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47584</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48596</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16333</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28234</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.53586</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.21368</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5394500000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5846699999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.91459</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5625399999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6387699999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57721</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49639</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52566</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45853</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34231</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.36882</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.25881</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09691</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17398</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.17779</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21798</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50924</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11933</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24237</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21657</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23638</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26471</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12504</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.21373</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.6724600000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47239</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29912</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04745000000000001</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03889</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04944</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04529</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03622</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04717</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04635</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04982</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04767</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04715</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21833</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04517</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04971</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00306</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01232</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15512</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05531</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11284</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.67679</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44468</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42199</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04543999999999999</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09787999999999999</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04393</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04579</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04565</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04554</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04708</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04501</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04776</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14285</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2689</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33536</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31743</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40422</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17241</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15945</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21402</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38391</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42875</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41578</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91523</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86525</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2979</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8902899999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6322000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18987</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87012</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5390199999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33364</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03486</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5335299999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79325</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52934</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77527</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77935</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87705</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87505</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49528</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40269</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20979</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62462</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53904</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49852</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5853700000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4269</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6014400000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6616799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47355</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5822999999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8778899999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62782</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8747200000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8572799999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8650599999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44293</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46014</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41189</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35324</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91506</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46334</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40917</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16656</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19897</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19027</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43139</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59449</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88974</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32721</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13583</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69716</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78711</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64258</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5762999999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49858</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41177</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42662</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44878</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39577</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43267</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41237</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49158</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.94159</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.61691</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.25331</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.21669</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.98388</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69974</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.66692</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.25947</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.40723</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38298</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44489</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.52173</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57439</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46131</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74272</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46325</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4362200000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32326</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42082</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.48173</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.89247</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16344</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.16797</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.16517</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17486</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.93667</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.92963</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14975</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15751</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14995</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15701</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.39452</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16156</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43896</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44176</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40142</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34815</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5348200000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4218</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41397</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32757</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29891</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29559</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27224</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20337</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24408</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28865</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24269</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24521</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35958</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41803</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.41834</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43849</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.06290999999999999</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.27958</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24926</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12041</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25403</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69838</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52616</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24342</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28211</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36202</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36601</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4244</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65742</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76571</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45191</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45676</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34438</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35143</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.27635</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.19013</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20072</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28029</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21942</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.17283</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.41046</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6402899999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60823</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5959</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46477</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.6648200000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47206</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8224199999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.48921</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.56679</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4749</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35965</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5362100000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48474</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49129</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40718</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39312</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44809</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55686</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49757</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.79208</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46695</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44702</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43232</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5109399999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.65036</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.22004</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41679</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43906</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49206</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5121599999999999</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69917</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7304700000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.5179400000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.64564</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80987</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5902999999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5269199999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8393699999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77898</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62729</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6775800000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44835</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47028</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5554600000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44104</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45578</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45463</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39656</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37023</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39919</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39433</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38381</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04226</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44948</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46111</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11315</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.08805</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41689</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40727</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41647</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39008</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4081</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36452</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27801</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22529</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23051</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25799</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13906</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29411</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24949</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25035</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29187</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17099</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18313</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23003</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25115</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23395</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27633</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34899</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.24742</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23238</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16015</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.19798</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23273</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01819</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00095</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03255</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10901</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02113</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03906</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01327</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0368</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03319</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04726</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02459</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02231</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20451</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0489</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00141</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04918</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04896</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04913</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03508</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04909</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04887</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17615</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18871</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.22981</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26038</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27774</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28592</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27853</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3045</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27864</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11251</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5518200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.13165</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27803</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.2661</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29093</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25719</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23381</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22147</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24144</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20416</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.22906</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23463</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25473</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.26929</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21104</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.58447</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6305599999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.56876</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.12035</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23199</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17294</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09537000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10617</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22287</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.08887</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00066</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.01686</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.07912000000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16289</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02921</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.09762999999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.10637</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02723</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.07897</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09156</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09032999999999999</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3227</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54875</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48494</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37764</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14243</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27263</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50669</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32845</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.64786</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.6062000000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50519</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28751</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50345</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46685</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42343</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5714400000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4864</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45833</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36844</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48065</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40079</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46024</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40067</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.28444</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40539</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42359</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43583</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51391</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.58521</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.58999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5172899999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50885</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54859</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.73873</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9024</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5925499999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5904299999999999</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3984</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39901</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.373</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35063</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29295</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21784</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16753</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20779</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04226</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20962</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16798</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01106</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26451</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16497</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06245000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06191</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07869</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16667</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08392000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06087</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15603</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.57269</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30539</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4346</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35625</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8617400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.25021</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24515</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24224</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11333</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.05353</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.06991</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.10455</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.24554</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.09823999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01954</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02728</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.05316</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.19636</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.08724</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.23406</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28539</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.5011</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39097</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58882</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41382</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35797</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.62403</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36875</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45732</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22778</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22655</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.11287</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00369</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04764</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04756000000000001</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07776999999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03047</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06265</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09584999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19294</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.11896</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05571</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26037</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14403</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11614</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23457</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18223</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23227</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.23963</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20062</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36394</v>
       </c>
     </row>
   </sheetData>
